--- a/PointCloud_Project_Time_Plan_Viktor - Rough_Final (2).xlsx
+++ b/PointCloud_Project_Time_Plan_Viktor - Rough_Final (2).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ltuse-my.sharepoint.com/personal/viklio-3_student_ltu_se/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikto\Documents\GitHub\D7016B-IAI-eMaintenance-Part-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0904B9F-22CD-48C2-A5A3-DBD944F30730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{593E1CD1-ECFC-48EA-A25F-EE6CA0FBDCB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29910" yWindow="1275" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>Project: Point Cloud Processing - Extracting Railway Track Geometry</t>
   </si>
@@ -209,9 +209,6 @@
     <t>2.3 Research about Catmul-rom and update report</t>
   </si>
   <si>
-    <t>2.4 Load data and first attempt at analyzing it</t>
-  </si>
-  <si>
     <t>3.2 Clean the data and noise points</t>
   </si>
   <si>
@@ -228,6 +225,12 @@
   </si>
   <si>
     <t>4.4 Explorative study - suggest how future studies could build upon this and these findings</t>
+  </si>
+  <si>
+    <t>2.4 Load data and first attempts</t>
+  </si>
+  <si>
+    <t>will be delayed</t>
   </si>
 </sst>
 </file>
@@ -454,18 +457,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -729,74 +732,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P55"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.88671875" customWidth="1"/>
-    <col min="4" max="4" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.21875" customWidth="1"/>
-    <col min="13" max="13" width="13.5546875" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.85546875" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-    </row>
-    <row r="2" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-    </row>
-    <row r="5" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+    </row>
+    <row r="2" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="31"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+    </row>
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>1</v>
       </c>
@@ -817,117 +820,117 @@
       <c r="O5" s="39"/>
       <c r="P5" s="25"/>
     </row>
-    <row r="6" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="36" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="37"/>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="I6" s="34" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="I6" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
       <c r="P6" s="22"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32" t="s">
+      <c r="C7" s="31"/>
+      <c r="D7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
       <c r="P7" s="22"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D8" s="32" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D8" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
       <c r="P8" s="22"/>
     </row>
-    <row r="9" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="34"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
       <c r="P9" s="22"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>46273</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="34"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D11" s="32" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="D11" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="34"/>
-    </row>
-    <row r="12" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
         <v>15</v>
       </c>
@@ -937,15 +940,15 @@
       <c r="E12" s="40"/>
       <c r="F12" s="40"/>
       <c r="G12" s="40"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" s="10">
         <v>46325</v>
       </c>
@@ -955,15 +958,15 @@
       <c r="E13" s="40"/>
       <c r="F13" s="40"/>
       <c r="G13" s="40"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B15" s="9"/>
       <c r="C15" t="s">
         <v>16</v>
@@ -972,29 +975,29 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
       <c r="C16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="16"/>
       <c r="C17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B19" s="6"/>
       <c r="C19" s="3" t="s">
         <v>19</v>
@@ -1018,7 +1021,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>1</v>
       </c>
@@ -1038,17 +1041,17 @@
       <c r="G20" s="20">
         <v>46274</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="17" t="s">
         <v>24</v>
@@ -1066,15 +1069,15 @@
       <c r="G21" s="19">
         <v>46275</v>
       </c>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="33"/>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="33"/>
-    </row>
-    <row r="22" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+      <c r="L21" s="30"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="30"/>
+      <c r="O21" s="30"/>
+    </row>
+    <row r="22" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="C22" s="17" t="s">
         <v>25</v>
@@ -1092,15 +1095,15 @@
       <c r="G22" s="27">
         <v>46282</v>
       </c>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="33"/>
-      <c r="M22" s="33"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="33"/>
-    </row>
-    <row r="23" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+    </row>
+    <row r="23" spans="2:15" ht="45" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="C23" s="23" t="s">
         <v>45</v>
@@ -1118,15 +1121,15 @@
       <c r="G23" s="19">
         <v>46282</v>
       </c>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="33"/>
-      <c r="M23" s="33"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="33"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
       <c r="C24" s="17" t="s">
         <v>26</v>
@@ -1144,15 +1147,15 @@
       <c r="G24" s="28">
         <v>46283</v>
       </c>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="33"/>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="C25" s="23" t="s">
         <v>43</v>
@@ -1170,15 +1173,15 @@
       <c r="G25" s="19">
         <v>46283</v>
       </c>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B26" s="7"/>
       <c r="C26" s="18"/>
       <c r="D26" s="12"/>
@@ -1186,7 +1189,7 @@
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
     </row>
-    <row r="27" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="5">
         <v>2</v>
       </c>
@@ -1206,20 +1209,20 @@
       <c r="G27" s="20">
         <v>46283</v>
       </c>
-      <c r="H27" s="30" t="s">
+      <c r="H27" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="I27" s="34" t="s">
+      <c r="I27" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-    </row>
-    <row r="28" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+    </row>
+    <row r="28" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="23" t="s">
         <v>47</v>
@@ -1237,16 +1240,16 @@
       <c r="G28" s="19">
         <v>46288</v>
       </c>
-      <c r="H28" s="30"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="33"/>
-      <c r="M28" s="33"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="33"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H28" s="33"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+    </row>
+    <row r="29" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="5"/>
       <c r="C29" s="23" t="s">
         <v>57</v>
@@ -1267,18 +1270,18 @@
       <c r="H29" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
-      <c r="O29" s="33"/>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="C30" s="23" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D30" s="11">
         <v>1</v>
@@ -1294,15 +1297,15 @@
         <v>46296</v>
       </c>
       <c r="H30" s="29"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
-      <c r="O30" s="33"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="30"/>
+      <c r="O30" s="30"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="C31" s="17" t="s">
         <v>48</v>
@@ -1320,16 +1323,18 @@
       <c r="G31" s="19">
         <v>46300</v>
       </c>
-      <c r="H31" s="29"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
-      <c r="O31" s="33"/>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="H31" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B32" s="7"/>
       <c r="C32" s="18"/>
       <c r="D32" s="12"/>
@@ -1337,7 +1342,7 @@
       <c r="F32" s="21"/>
       <c r="G32" s="21"/>
     </row>
-    <row r="33" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="5">
         <v>3</v>
       </c>
@@ -1357,23 +1362,23 @@
       <c r="G33" s="20">
         <v>46300</v>
       </c>
-      <c r="I33" s="33" t="s">
+      <c r="I33" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="33"/>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
-      <c r="O33" s="33"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="30"/>
+      <c r="O33" s="30"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="C34" s="23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D34" s="11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E34" s="1">
         <f>G34-F34+1</f>
@@ -1385,21 +1390,21 @@
       <c r="G34" s="19">
         <v>46305</v>
       </c>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
-      <c r="M34" s="33"/>
-      <c r="N34" s="33"/>
-      <c r="O34" s="33"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="30"/>
+      <c r="O34" s="30"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="C35" s="23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D35" s="11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E35" s="1">
         <f>G35-F35+1</f>
@@ -1411,18 +1416,18 @@
       <c r="G35" s="19">
         <v>46309</v>
       </c>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="33"/>
-      <c r="N35" s="33"/>
-      <c r="O35" s="33"/>
-    </row>
-    <row r="36" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="30"/>
+      <c r="N35" s="30"/>
+      <c r="O35" s="30"/>
+    </row>
+    <row r="36" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="C36" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D36" s="11">
         <v>0</v>
@@ -1437,15 +1442,15 @@
       <c r="G36" s="19">
         <v>46310</v>
       </c>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+      <c r="O36" s="30"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B37" s="5"/>
       <c r="C37" s="17" t="s">
         <v>49</v>
@@ -1463,15 +1468,15 @@
       <c r="G37" s="19">
         <v>46311</v>
       </c>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="33"/>
-      <c r="L37" s="33"/>
-      <c r="M37" s="33"/>
-      <c r="N37" s="33"/>
-      <c r="O37" s="33"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B38" s="7"/>
       <c r="C38" s="18"/>
       <c r="D38" s="12"/>
@@ -1479,7 +1484,7 @@
       <c r="F38" s="21"/>
       <c r="G38" s="21"/>
     </row>
-    <row r="39" spans="2:15" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:15" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="5">
         <v>4</v>
       </c>
@@ -1499,20 +1504,20 @@
       <c r="G39" s="20">
         <v>46311</v>
       </c>
-      <c r="I39" s="33" t="s">
+      <c r="I39" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="30"/>
+      <c r="N39" s="30"/>
+      <c r="O39" s="30"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="C40" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D40" s="11">
         <v>0</v>
@@ -1527,18 +1532,18 @@
       <c r="G40" s="19">
         <v>46317</v>
       </c>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
-      <c r="N40" s="33"/>
-      <c r="O40" s="33"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B41" s="5"/>
       <c r="C41" s="23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D41" s="11">
         <v>0</v>
@@ -1553,18 +1558,18 @@
       <c r="G41" s="19">
         <v>46318</v>
       </c>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
-      <c r="M41" s="33"/>
-      <c r="N41" s="33"/>
-      <c r="O41" s="33"/>
-    </row>
-    <row r="42" spans="2:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="30"/>
+      <c r="N41" s="30"/>
+      <c r="O41" s="30"/>
+    </row>
+    <row r="42" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="C42" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D42" s="11">
         <v>0</v>
@@ -1579,15 +1584,15 @@
       <c r="G42" s="19">
         <v>46321</v>
       </c>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
-      <c r="O42" s="33"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="C43" s="23" t="s">
         <v>32</v>
@@ -1605,15 +1610,15 @@
       <c r="G43" s="19">
         <v>46321</v>
       </c>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
-      <c r="M43" s="33"/>
-      <c r="N43" s="33"/>
-      <c r="O43" s="33"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="C44" s="17" t="s">
         <v>33</v>
@@ -1631,15 +1636,15 @@
       <c r="G44" s="19">
         <v>46322</v>
       </c>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="33"/>
-      <c r="M44" s="33"/>
-      <c r="N44" s="33"/>
-      <c r="O44" s="33"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="30"/>
+      <c r="N44" s="30"/>
+      <c r="O44" s="30"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B45" s="7"/>
       <c r="C45" s="18"/>
       <c r="D45" s="12"/>
@@ -1647,7 +1652,7 @@
       <c r="F45" s="21"/>
       <c r="G45" s="21"/>
     </row>
-    <row r="46" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="5">
         <v>5</v>
       </c>
@@ -1667,17 +1672,17 @@
       <c r="G46" s="20">
         <v>46323</v>
       </c>
-      <c r="I46" s="33" t="s">
+      <c r="I46" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="33"/>
-      <c r="M46" s="33"/>
-      <c r="N46" s="33"/>
-      <c r="O46" s="33"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B47" s="7"/>
       <c r="C47" s="18"/>
       <c r="D47" s="12"/>
@@ -1685,7 +1690,7 @@
       <c r="F47" s="21"/>
       <c r="G47" s="21"/>
     </row>
-    <row r="48" spans="2:15" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:15" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="5">
         <v>6</v>
       </c>
@@ -1705,17 +1710,17 @@
       <c r="G48" s="19">
         <v>46321</v>
       </c>
-      <c r="I48" s="33" t="s">
+      <c r="I48" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="30"/>
+      <c r="N48" s="30"/>
+      <c r="O48" s="30"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B49" s="5"/>
       <c r="C49" s="17" t="s">
         <v>38</v>
@@ -1733,15 +1738,15 @@
       <c r="G49" s="19">
         <v>46323</v>
       </c>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="33"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="C50" s="17" t="s">
         <v>39</v>
@@ -1759,15 +1764,15 @@
       <c r="G50" s="20">
         <v>46323</v>
       </c>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="33"/>
-      <c r="N50" s="33"/>
-      <c r="O50" s="33"/>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="30"/>
+      <c r="N50" s="30"/>
+      <c r="O50" s="30"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="C51" s="17" t="s">
         <v>40</v>
@@ -1785,38 +1790,31 @@
       <c r="G51" s="20">
         <v>46325</v>
       </c>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="33"/>
-      <c r="M51" s="33"/>
-      <c r="N51" s="33"/>
-      <c r="O51" s="33"/>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="30"/>
+      <c r="N51" s="30"/>
+      <c r="O51" s="30"/>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C53" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C54" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C55" s="26" t="s">
         <v>50</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="I48:O51"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="I27:O31"/>
-    <mergeCell ref="I33:O37"/>
-    <mergeCell ref="I39:O44"/>
-    <mergeCell ref="I46:O46"/>
-    <mergeCell ref="H27:H28"/>
     <mergeCell ref="A1:P3"/>
     <mergeCell ref="D16:G17"/>
     <mergeCell ref="I20:O25"/>
@@ -1832,6 +1830,13 @@
     <mergeCell ref="D9:G9"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="D11:G11"/>
+    <mergeCell ref="I48:O51"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="I27:O31"/>
+    <mergeCell ref="I33:O37"/>
+    <mergeCell ref="I39:O44"/>
+    <mergeCell ref="I46:O46"/>
+    <mergeCell ref="H27:H28"/>
   </mergeCells>
   <conditionalFormatting sqref="D20:D51">
     <cfRule type="dataBar" priority="3">
@@ -1860,6 +1865,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100381E38323335DD41A90A4B5E9CB3C6CA" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b3634e145e5b32cd575c0695baa724db">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="76ca4f91-eb2a-4106-a0a0-28221db387de" xmlns:ns4="ecef2fa7-c193-44c0-bcae-1928c0cae763" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a10e196ece3972ff9737fec60bf519e" ns3:_="" ns4:_="">
     <xsd:import namespace="76ca4f91-eb2a-4106-a0a0-28221db387de"/>
@@ -2054,15 +2068,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2072,6 +2077,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{012F3B03-7687-4D76-94D0-DEE6D0263AEB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B087F1B-F6A0-4F64-9AD0-ABAFD232CFD9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2086,14 +2099,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{012F3B03-7687-4D76-94D0-DEE6D0263AEB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
